--- a/My_Professional_Reviews/UAS-5_Skor.xlsx
+++ b/My_Professional_Reviews/UAS-5_Skor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Azikra\Documents\GitHub\all-about-me\My_Professional_Reviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC3154A-BD89-493B-BB05-E49D9C2E4A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924F7A89-8081-4A6C-85D5-8CB8F827D2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="UAS_1_My_Concepts" sheetId="2" r:id="rId1"/>
@@ -713,20 +713,20 @@
         <v>27</v>
       </c>
       <c r="C5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1757,8 +1757,8 @@
       <c r="AP82" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F82" xr:uid="{B0F61EF9-DC4B-1D4B-A700-95D0E3F024E2}">
+  <dataValidations xWindow="459" yWindow="346" count="1">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F4 C6:F82" xr:uid="{B0F61EF9-DC4B-1D4B-A700-95D0E3F024E2}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -1886,7 +1886,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G10" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
+        <f t="shared" ref="G3:G9" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
         <v>4.25</v>
       </c>
       <c r="L3" s="4"/>
@@ -1936,20 +1936,20 @@
         <v>27</v>
       </c>
       <c r="C5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(COUNT(C5:F5)=0,"",AVERAGE(C5:F5))</f>
+        <v>0</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="G11" s="4" t="str">
-        <f t="shared" ref="G3:G66" si="1">IF(COUNT(C11:F11)=0,"",AVERAGE(C11:F11))</f>
+        <f t="shared" ref="G11:G66" si="1">IF(COUNT(C11:F11)=0,"",AVERAGE(C11:F11))</f>
         <v/>
       </c>
       <c r="L11" s="4"/>
@@ -2981,7 +2981,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F82" xr:uid="{291081A7-738A-49C0-9F8A-57EBA5F49046}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F4 C6:F82" xr:uid="{291081A7-738A-49C0-9F8A-57EBA5F49046}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -3109,7 +3109,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G10" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
+        <f t="shared" ref="G3:G9" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
         <v>4.75</v>
       </c>
       <c r="L3" s="4"/>
@@ -3159,20 +3159,20 @@
         <v>27</v>
       </c>
       <c r="C5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="G11" s="4" t="str">
-        <f t="shared" ref="G3:G66" si="1">IF(COUNT(C11:F11)=0,"",AVERAGE(C11:F11))</f>
+        <f t="shared" ref="G11:G66" si="1">IF(COUNT(C11:F11)=0,"",AVERAGE(C11:F11))</f>
         <v/>
       </c>
       <c r="L11" s="4"/>
@@ -4204,12 +4204,13 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F82" xr:uid="{B82A1BB6-6C75-4C86-932B-593EF645695D}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F4 C6:F82" xr:uid="{B82A1BB6-6C75-4C86-932B-593EF645695D}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4382,20 +4383,20 @@
         <v>27</v>
       </c>
       <c r="C5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -4480,10 +4481,7 @@
       <c r="B10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="G10" s="4"/>
       <c r="L10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="V10" s="4"/>
@@ -5430,11 +5428,12 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F82" xr:uid="{7566A2DC-1040-427C-8A1C-1B8E6819BD6A}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F4 C6:F82" xr:uid="{7566A2DC-1040-427C-8A1C-1B8E6819BD6A}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>